--- a/username.xlsx
+++ b/username.xlsx
@@ -16,12 +16,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
   <si>
     <t>name</t>
   </si>
   <si>
     <t>password</t>
+  </si>
+  <si>
+    <t>abdo</t>
   </si>
 </sst>
 </file>
@@ -360,15 +363,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -377,6 +380,30 @@
       </c>
       <c r="B2">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>123</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
